--- a/dados/Dados agregados/B3_dados_agregados.xlsx
+++ b/dados/Dados agregados/B3_dados_agregados.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Índice" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Índice" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tab 1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -252,29 +252,29 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="3638445"/>
+    <ext cx="5905500" cy="3661351"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -648,13 +648,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -685,6 +686,11 @@
           <t>17/10 Paralela</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>30/10 Paralela</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -701,6 +707,9 @@
       <c r="D3" s="10" t="n">
         <v>2.47</v>
       </c>
+      <c r="E3" s="10" t="n">
+        <v>2.65</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -717,6 +726,9 @@
       <c r="D4" s="4" t="n">
         <v>3</v>
       </c>
+      <c r="E4" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -733,6 +745,9 @@
       <c r="D5" s="4" t="n">
         <v>13</v>
       </c>
+      <c r="E5" s="4" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -752,6 +767,10 @@
         <f>IFERROR(D5/D3,"")</f>
         <v/>
       </c>
+      <c r="E6" s="10">
+        <f>IFERROR(E5/E3,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -771,6 +790,10 @@
         <f>IFERROR(D5/D4,"")</f>
         <v/>
       </c>
+      <c r="E7" s="10">
+        <f>IFERROR(E5/E4,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -787,6 +810,9 @@
       <c r="D8" s="10" t="n">
         <v>53.3</v>
       </c>
+      <c r="E8" s="10" t="n">
+        <v>103.8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -803,6 +829,9 @@
       <c r="D9" s="4" t="n">
         <v>4</v>
       </c>
+      <c r="E9" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -819,6 +848,9 @@
       <c r="D10" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="E10" s="4" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -838,6 +870,10 @@
         <f>IFERROR(D10/D9,"")</f>
         <v/>
       </c>
+      <c r="E11" s="10">
+        <f>IFERROR(E10/E9,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -854,6 +890,9 @@
       <c r="D12" s="10" t="n">
         <v>99.5</v>
       </c>
+      <c r="E12" s="10" t="n">
+        <v>136.9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -870,6 +909,9 @@
       <c r="D13" s="11" t="n">
         <v>91.5</v>
       </c>
+      <c r="E13" s="11" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -887,7 +929,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
